--- a/assets/thongke_template.xlsx
+++ b/assets/thongke_template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7811B7-22E7-41A6-82F4-E6EFC8187AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CECF6153-F1A7-4A27-A114-9FE32B73974E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22545" yWindow="360" windowWidth="22440" windowHeight="14625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thống kê" sheetId="1" r:id="rId1"/>
@@ -386,190 +386,358 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
-<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
-  <cx:chartData>
-    <cx:data id="0">
-      <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.0</cx:f>
-      </cx:strDim>
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.1</cx:f>
-      </cx:numDim>
-    </cx:data>
-    <cx:data id="1">
-      <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.0</cx:f>
-      </cx:strDim>
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.2</cx:f>
-      </cx:numDim>
-    </cx:data>
-    <cx:data id="2">
-      <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.0</cx:f>
-      </cx:strDim>
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.3</cx:f>
-      </cx:numDim>
-    </cx:data>
-    <cx:data id="3">
-      <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.0</cx:f>
-      </cx:strDim>
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.4</cx:f>
-      </cx:numDim>
-    </cx:data>
-    <cx:data id="4">
-      <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.0</cx:f>
-      </cx:strDim>
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.5</cx:f>
-      </cx:numDim>
-    </cx:data>
-  </cx:chartData>
-  <cx:chart>
-    <cx:title pos="t" align="ctr" overlay="0"/>
-    <cx:plotArea>
-      <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{97BEA9E0-5348-4FB1-9CCB-E4544015D4AC}" formatIdx="0">
-          <cx:dataLabels>
-            <cx:visibility seriesName="0" categoryName="0" value="1"/>
-          </cx:dataLabels>
-          <cx:dataId val="0"/>
-          <cx:layoutPr>
-            <cx:aggregation/>
-          </cx:layoutPr>
-          <cx:axisId val="1"/>
-        </cx:series>
-        <cx:series layoutId="paretoLine" ownerIdx="0" uniqueId="{AAE32702-CBAE-43CE-B646-1885A5B66597}" formatIdx="1">
-          <cx:axisId val="2"/>
-        </cx:series>
-        <cx:series layoutId="clusteredColumn" hidden="1" uniqueId="{3B47C815-7FCD-4244-ADDA-7E10DA87C3BF}" formatIdx="2">
-          <cx:dataLabels/>
-          <cx:dataId val="1"/>
-          <cx:layoutPr>
-            <cx:aggregation/>
-          </cx:layoutPr>
-          <cx:axisId val="1"/>
-        </cx:series>
-        <cx:series layoutId="paretoLine" ownerIdx="2" uniqueId="{79EDD418-E702-440D-9A1B-63E78D43D36D}" formatIdx="3">
-          <cx:axisId val="2"/>
-        </cx:series>
-        <cx:series layoutId="clusteredColumn" hidden="1" uniqueId="{D1A33552-3FB9-457F-B8AD-BAF6BE22CD47}" formatIdx="4">
-          <cx:dataId val="2"/>
-          <cx:layoutPr>
-            <cx:aggregation/>
-          </cx:layoutPr>
-          <cx:axisId val="1"/>
-        </cx:series>
-        <cx:series layoutId="paretoLine" ownerIdx="4" uniqueId="{518C2D0C-4FE3-4010-88E0-3FE3715135E1}" formatIdx="5">
-          <cx:axisId val="2"/>
-        </cx:series>
-        <cx:series layoutId="clusteredColumn" hidden="1" uniqueId="{0D76ADDB-BC3F-4D6F-9D10-58A295CFCC00}" formatIdx="6">
-          <cx:dataId val="3"/>
-          <cx:layoutPr>
-            <cx:aggregation/>
-          </cx:layoutPr>
-          <cx:axisId val="1"/>
-        </cx:series>
-        <cx:series layoutId="paretoLine" ownerIdx="6" uniqueId="{00714B07-9E09-4C28-9D81-5E2494F8515F}" formatIdx="7">
-          <cx:axisId val="2"/>
-        </cx:series>
-        <cx:series layoutId="clusteredColumn" hidden="1" uniqueId="{8A6C668C-682B-4D23-B202-7F0FE1C947E6}" formatIdx="8">
-          <cx:dataId val="4"/>
-          <cx:layoutPr>
-            <cx:aggregation/>
-          </cx:layoutPr>
-          <cx:axisId val="1"/>
-        </cx:series>
-        <cx:series layoutId="paretoLine" ownerIdx="8" uniqueId="{126C27EA-FF0B-4355-876E-A23114A1F430}" formatIdx="9">
-          <cx:axisId val="2"/>
-        </cx:series>
-      </cx:plotAreaRegion>
-      <cx:axis id="0">
-        <cx:catScaling gapWidth="0.180000007"/>
-        <cx:majorTickMarks type="in"/>
-        <cx:minorTickMarks type="in"/>
-        <cx:tickLabels/>
-        <cx:numFmt formatCode="#,##0;-#,##0" sourceLinked="0"/>
-        <cx:txPr>
-          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="7.9247594050743664E-2"/>
+          <c:y val="0.19797141844525473"/>
+          <c:w val="0.89019685039370078"/>
+          <c:h val="0.58438406689453415"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Thống kê'!$B$4:$B$17</c:f>
+              <c:strCache>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>19134A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19134D</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19134G</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19134I</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19134L</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>19134M</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>19134N</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19134O</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19134Q</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19134R</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>19134U</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>19134V</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>19134W</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>19134X</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Thống kê'!$C$4:$C$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>551</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8261-4FF9-B179-BA1985EAB015}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="974518336"/>
+        <c:axId val="1511213632"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="974518336"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr algn="ctr" rtl="0">
-              <a:defRPr>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000">
+                  <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
-                  </a:sysClr>
+                  </a:schemeClr>
                 </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1511213632"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1511213632"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:sysClr>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:endParaRPr>
-          </a:p>
-        </cx:txPr>
-      </cx:axis>
-      <cx:axis id="1">
-        <cx:valScaling/>
-        <cx:majorGridlines/>
-        <cx:tickLabels/>
-      </cx:axis>
-      <cx:axis id="2">
-        <cx:valScaling max="1" min="0"/>
-        <cx:units unit="percentage"/>
-        <cx:tickLabels/>
-        <cx:spPr>
-          <a:effectLst>
-            <a:softEdge rad="0"/>
-          </a:effectLst>
-        </cx:spPr>
-        <cx:txPr>
-          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr algn="ctr" rtl="0">
-              <a:defRPr>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000">
+                  <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
-                  </a:sysClr>
+                  </a:schemeClr>
                 </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:sysClr>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:endParaRPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
-        </cx:txPr>
-      </cx:axis>
-    </cx:plotArea>
-  </cx:chart>
-</cx:chartSpace>
+        </c:txPr>
+        <c:crossAx val="974518336"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -613,7 +781,7 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="366">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -624,7 +792,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -647,7 +815,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
@@ -670,7 +838,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -678,11 +846,11 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:dataLabel>
   <cs:dataLabelCallout>
     <cs:lnRef idx="0"/>
@@ -707,14 +875,14 @@
         </a:solidFill>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900"/>
+    <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
       <a:spAutoFit/>
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
@@ -729,7 +897,7 @@
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
@@ -746,7 +914,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -761,8 +929,10 @@
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
@@ -775,7 +945,7 @@
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
       </a:ln>
     </cs:spPr>
@@ -785,13 +955,13 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="9525" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -810,16 +980,18 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:dataTable>
   <cs:downBar>
     <cs:lnRef idx="0"/>
@@ -890,6 +1062,12 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
@@ -921,8 +1099,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -977,7 +1155,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
   <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
@@ -1005,30 +1183,22 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat">
-        <a:solidFill>
-          <a:srgbClr val="D9D9D9"/>
         </a:solidFill>
         <a:round/>
       </a:ln>
@@ -1044,7 +1214,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400"/>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -1060,7 +1230,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDash"/>
+        <a:prstDash val="sysDot"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -1074,7 +1244,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:trendlineLabel>
   <cs:upBar>
     <cs:lnRef idx="0"/>
@@ -1107,7 +1277,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
     <cs:lnRef idx="0"/>
@@ -1116,6 +1286,12 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -1124,80 +1300,38 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>176212</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>61912</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>147637</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="3" name="Chart 2">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3F67C63-57D9-8540-E3A3-6DEC3919B424}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="10106025" y="4700587"/>
-              <a:ext cx="4648200" cy="2743200"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100"/>
-                <a:t>This chart isn't available in your version of Excel.
-Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CA7B8CC-9EE9-872C-4B88-97DE57A3E43F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
